--- a/artfynd/S 5806-2022 artfynd.xlsx
+++ b/artfynd/S 5806-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AZ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74029167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580738</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580628</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63181478</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580744</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63201297</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1865,6 +1915,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539873</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1976,6 +2031,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580687</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2106,6 +2166,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827717</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2212,6 +2277,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580743</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2309,6 +2379,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199803</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2415,6 +2490,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580740</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2541,6 +2621,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537474</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2667,6 +2752,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63203035</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2793,6 +2883,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63203150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2919,6 +3014,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539574</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3045,6 +3145,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539576</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3171,6 +3276,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539577</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3297,6 +3407,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539655</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3423,6 +3538,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539690</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3549,6 +3669,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189581</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3675,6 +3800,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189600</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3801,6 +3931,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538317</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3927,6 +4062,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538318</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4053,6 +4193,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538354</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4179,6 +4324,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225602</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4305,6 +4455,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538816</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4406,6 +4561,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580574</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4521,6 +4681,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580671</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4631,6 +4796,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103039391</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4746,6 +4916,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103058653</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4861,6 +5036,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103075702</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4971,6 +5151,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103103559</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5077,6 +5262,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580481</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5183,6 +5373,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580482</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5284,6 +5479,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580593</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5385,6 +5585,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580754</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5492,6 +5697,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74464038</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5598,6 +5808,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580698</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5704,6 +5919,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580564</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5810,6 +6030,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580565</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5916,6 +6141,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580566</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6022,6 +6252,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580567</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6133,6 +6368,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580652</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6244,6 +6484,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580653</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6345,6 +6590,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580533</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6446,6 +6696,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580535</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6548,6 +6803,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1290272</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6663,6 +6923,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580683</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6774,6 +7039,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1761268</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6885,6 +7155,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580575</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6996,6 +7271,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580576</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7103,6 +7383,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199840</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7210,6 +7495,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199841</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7317,6 +7607,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199842</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7419,6 +7714,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199798</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7545,6 +7845,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538377</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7675,6 +7980,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827713</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7800,6 +8110,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828508</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7919,6 +8234,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91275039</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8042,6 +8362,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91275071</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8172,6 +8497,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827723</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8291,6 +8621,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91275059</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8406,6 +8741,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580626</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8541,6 +8881,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98827722</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8667,6 +9012,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184302</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8793,6 +9143,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537513</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8916,6 +9271,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91275031</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9051,6 +9411,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98829675</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9181,6 +9546,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98829677</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9316,6 +9686,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98829683</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9442,6 +9817,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63201017</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9568,6 +9948,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539862</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9689,6 +10074,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828515</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9810,6 +10200,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828516</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9931,6 +10326,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828517</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10052,6 +10452,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828519</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10173,6 +10578,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828520</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10294,6 +10704,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828521</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10415,6 +10830,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123512</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10536,6 +10956,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123517</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10655,6 +11080,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91275082</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10761,6 +11191,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580524</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10868,6 +11303,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199794</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10975,6 +11415,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199925</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11108,6 +11553,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68798902</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11234,6 +11684,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537480</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11360,6 +11815,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202402</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11486,6 +11946,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539675</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11612,6 +12077,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189582</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11738,6 +12208,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189583</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11864,6 +12339,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538343</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11990,6 +12470,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225909</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12116,6 +12601,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538815</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12227,6 +12717,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73983185</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12338,6 +12833,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552781</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12439,6 +12939,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580548</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12540,6 +13045,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580633</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12641,6 +13151,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580634</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12742,6 +13257,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580636</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12844,6 +13364,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199823</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12946,6 +13471,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199824</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13052,6 +13582,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580723</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13158,6 +13693,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580724</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13264,6 +13804,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580725</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13365,8 +13910,124 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>